--- a/Paytm UPI Growth Challenge 2026 — Raw Short VOC Responses.xlsx
+++ b/Paytm UPI Growth Challenge 2026 — Raw Short VOC Responses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53276014-2E1E-4484-9CB8-5EE2936E22B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B26B5E5-0700-4842-A332-643FC2BDE256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="396">
   <si>
     <t>Timestamp</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>12. Would you be open to a 15-minute follow-up conversation about your UPI habits?</t>
-  </si>
-  <si>
-    <t>13. If yes, please share your preferred contact (phone/email).</t>
   </si>
   <si>
     <t>College student</t>
@@ -1204,6 +1201,18 @@
   </si>
   <si>
     <t xml:space="preserve">Food / cafés / restaurants, </t>
+  </si>
+  <si>
+    <t>Lakhimpur khiri</t>
+  </si>
+  <si>
+    <t>If it made my daily payment faster and esair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If it made my daily payments faster and easier </t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1333,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:N112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Form_Responses" displayName="Form_Responses" ref="A1:N114">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="1. Which best describes you?"/>
@@ -1339,7 +1348,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="10. What is the BIGGEST reason you do NOT use Paytm for more of your UPI payments?"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="11. In ONE sentence: what would make you use Paytm more?"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="12. Would you be open to a 15-minute follow-up conversation about your UPI habits?"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="13. If yes, please share your preferred contact (phone/email)."/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1547,7 +1556,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.88671875" customWidth="1"/>
@@ -1557,7 +1566,9 @@
     <col min="5" max="5" width="31.44140625" customWidth="1"/>
     <col min="6" max="7" width="37.6640625" customWidth="1"/>
     <col min="8" max="8" width="32.77734375" customWidth="1"/>
-    <col min="9" max="14" width="37.6640625" customWidth="1"/>
+    <col min="9" max="12" width="37.6640625" customWidth="1"/>
+    <col min="13" max="13" width="71.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="37.6640625" customWidth="1"/>
     <col min="15" max="20" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1602,7 +1613,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1610,40 +1621,40 @@
         <v>46276.908094375001</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="M2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="3"/>
     </row>
@@ -1652,84 +1663,82 @@
         <v>46276.91224096065</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="M3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N3" s="3">
-        <v>8839104266</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N3" s="3"/>
     </row>
     <row r="4" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46276.918133495376</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="M4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1737,40 +1746,40 @@
         <v>46276.919483634258</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="M5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1778,40 +1787,40 @@
         <v>46276.919861018519</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1819,128 +1828,124 @@
         <v>46276.920311064816</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N7" s="3">
-        <v>7518228908</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46276.920860613427</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="M8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N8" s="3">
-        <v>9415432196</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46276.921635347222</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="M9" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1948,84 +1953,82 @@
         <v>46276.926152291664</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46276.926177777779</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="M11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2033,84 +2036,82 @@
         <v>46276.92766799769</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="M12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46276.930782673611</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="M13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2118,128 +2119,124 @@
         <v>46276.932790208331</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="M14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46276.93613047454</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="M15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="3">
-        <v>6386901021</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="N15" s="3"/>
     </row>
     <row r="16" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46276.936206076389</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="M16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2247,40 +2244,40 @@
         <v>46276.937901053243</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="M17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N17" s="3"/>
     </row>
@@ -2289,40 +2286,40 @@
         <v>46276.939151307874</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="M18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2330,40 +2327,40 @@
         <v>46276.93964744213</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="M19" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N19" s="3"/>
     </row>
@@ -2372,40 +2369,40 @@
         <v>46276.940139675928</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="M20" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2413,40 +2410,40 @@
         <v>46276.941682500001</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="M21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N21" s="3"/>
     </row>
@@ -2455,40 +2452,40 @@
         <v>46276.942892615742</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="M22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N22" s="3"/>
     </row>
@@ -2497,40 +2494,40 @@
         <v>46276.943596041667</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="M23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N23" s="3"/>
     </row>
@@ -2539,40 +2536,40 @@
         <v>46276.943715983798</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="M24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N24" s="3"/>
     </row>
@@ -2581,40 +2578,40 @@
         <v>46276.943753819447</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="M25" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N25" s="3"/>
     </row>
@@ -2623,40 +2620,40 @@
         <v>46276.944238252312</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="M26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N26" s="3"/>
     </row>
@@ -2665,40 +2662,40 @@
         <v>46276.944541273144</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I27" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="K27" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N27" s="3"/>
     </row>
@@ -2707,40 +2704,40 @@
         <v>46276.94504554398</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K28" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N28" s="3"/>
     </row>
@@ -2749,40 +2746,40 @@
         <v>46276.945818946755</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="H29" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="M29" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N29" s="3"/>
     </row>
@@ -2791,40 +2788,40 @@
         <v>46276.946920902774</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="M30" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N30" s="3"/>
     </row>
@@ -2833,40 +2830,40 @@
         <v>46276.94882853009</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H31" s="3" t="s">
+      <c r="I31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="K31" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="M31" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2874,40 +2871,40 @@
         <v>46276.951074814817</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="K32" s="3" t="s">
+      <c r="L32" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="M32" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N32" s="3"/>
     </row>
@@ -2916,40 +2913,40 @@
         <v>46276.951086134257</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K33" s="3" t="s">
+      <c r="L33" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="M33" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2957,40 +2954,40 @@
         <v>46276.952618460651</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="L34" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="M34" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2998,40 +2995,40 @@
         <v>46276.954732291662</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="M35" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3039,40 +3036,40 @@
         <v>46276.955456643518</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="I36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="M36" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3080,40 +3077,40 @@
         <v>46276.957007152778</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K37" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="L37" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="M37" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N37" s="3"/>
     </row>
@@ -3122,40 +3119,40 @@
         <v>46276.957320902773</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="M38" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N38" s="3"/>
     </row>
@@ -3164,40 +3161,40 @@
         <v>46276.959251076391</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K39" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="M39" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N39" s="3"/>
     </row>
@@ -3206,40 +3203,40 @@
         <v>46276.96640798611</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="I40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="K40" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="M40" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3247,40 +3244,40 @@
         <v>46276.966748784718</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H41" s="3" t="s">
+      <c r="I41" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="M41" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3288,40 +3285,40 @@
         <v>46276.975796909726</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H42" s="3" t="s">
+      <c r="I42" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="K42" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="M42" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N42" s="3"/>
     </row>
@@ -3330,40 +3327,40 @@
         <v>46276.978334224536</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H43" s="3" t="s">
+      <c r="I43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K43" s="3" t="s">
+      <c r="L43" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="M43" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3371,40 +3368,40 @@
         <v>46276.982120474539</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>219</v>
-      </c>
       <c r="M44" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N44" s="3"/>
     </row>
@@ -3413,40 +3410,40 @@
         <v>46276.984019884258</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N45" s="3"/>
     </row>
@@ -3455,40 +3452,40 @@
         <v>46276.984050462968</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H46" s="3" t="s">
+      <c r="I46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J46" s="3" t="s">
+      <c r="K46" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="L46" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="M46" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N46" s="3"/>
     </row>
@@ -3497,40 +3494,40 @@
         <v>46276.992092060187</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="M47" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3538,40 +3535,40 @@
         <v>46277.002589432872</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="J48" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="K48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="M48" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3579,40 +3576,40 @@
         <v>46277.006613599537</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I49" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="L49" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="M49" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3620,40 +3617,40 @@
         <v>46277.017987870371</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="3" t="s">
+      <c r="K50" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="M50" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3661,40 +3658,40 @@
         <v>46277.019293310186</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H51" s="3" t="s">
+      <c r="I51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K51" s="3" t="s">
+      <c r="L51" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="L51" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="M51" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3702,40 +3699,40 @@
         <v>46277.023426111111</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H52" s="3" t="s">
+      <c r="I52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="M52" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3743,40 +3740,40 @@
         <v>46277.037709560187</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J53" s="3" t="s">
+      <c r="K53" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="K53" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="M53" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3784,40 +3781,40 @@
         <v>46277.050522152778</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I54" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="L54" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3825,40 +3822,40 @@
         <v>46277.066936331015</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" s="3" t="s">
+      <c r="I55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="M55" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3866,40 +3863,40 @@
         <v>46277.248250347227</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H56" s="3" t="s">
+      <c r="I56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="L56" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="M56" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N56" s="3"/>
     </row>
@@ -3908,40 +3905,40 @@
         <v>46277.256225844903</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="M57" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N57" s="3"/>
     </row>
@@ -3950,40 +3947,40 @@
         <v>46277.279737881945</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H58" s="3" t="s">
+      <c r="I58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="M58" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N58" s="3"/>
     </row>
@@ -3992,40 +3989,40 @@
         <v>46277.282854108795</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="M59" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4033,40 +4030,40 @@
         <v>46277.294692881944</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="H60" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N60" s="3"/>
     </row>
@@ -4075,40 +4072,40 @@
         <v>46277.29944563657</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J61" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J61" s="3" t="s">
+      <c r="K61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L61" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="K61" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="M61" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4116,40 +4113,40 @@
         <v>46277.301044780092</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="H62" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N62" s="3"/>
     </row>
@@ -4158,40 +4155,40 @@
         <v>46277.304316805559</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H63" s="3" t="s">
+      <c r="I63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>278</v>
-      </c>
       <c r="M63" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N63" s="3"/>
     </row>
@@ -4200,40 +4197,40 @@
         <v>46277.308310381944</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L64" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="M64" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N64" s="3"/>
     </row>
@@ -4242,40 +4239,40 @@
         <v>46277.336958495369</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I65" s="3" t="s">
+      <c r="J65" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L65" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="M65" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4283,40 +4280,40 @@
         <v>46277.340253310183</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H66" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="M66" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4324,40 +4321,40 @@
         <v>46277.345849490739</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J67" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="K67" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="M67" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4365,40 +4362,40 @@
         <v>46277.348763715279</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H68" s="3" t="s">
+      <c r="I68" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L68" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="I68" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="M68" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4406,40 +4403,40 @@
         <v>46277.351122881941</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H69" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" s="3" t="s">
+      <c r="I69" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="J69" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="J69" s="3" t="s">
+      <c r="K69" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="K69" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="M69" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4447,40 +4444,40 @@
         <v>46277.365258784717</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H70" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L70" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="M70" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,40 +4485,40 @@
         <v>46277.372796666663</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D71" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>300</v>
-      </c>
       <c r="M71" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4529,40 +4526,40 @@
         <v>46277.375042604166</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L72" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="M72" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4570,40 +4567,40 @@
         <v>46277.375467777776</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H73" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N73" s="3"/>
     </row>
@@ -4612,40 +4609,40 @@
         <v>46277.377047476853</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4653,40 +4650,40 @@
         <v>46277.383636053244</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J75" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L75" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="K75" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="M75" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N75" s="3"/>
     </row>
@@ -4695,40 +4692,40 @@
         <v>46277.417527638885</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H76" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>308</v>
-      </c>
       <c r="K76" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L76" s="3">
         <v>200000</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N76" s="3"/>
     </row>
@@ -4737,40 +4734,40 @@
         <v>46277.433556388889</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4778,40 +4775,40 @@
         <v>46277.434776643524</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H78" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N78" s="3"/>
     </row>
@@ -4820,40 +4817,40 @@
         <v>46277.436278090274</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H79" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N79" s="3"/>
     </row>
@@ -4862,40 +4859,40 @@
         <v>46277.447565358802</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H80" s="3" t="s">
+      <c r="I80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K80" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="I80" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K80" s="3" t="s">
+      <c r="L80" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="L80" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="M80" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4903,40 +4900,40 @@
         <v>46277.454018657409</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="E81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H81" s="3" t="s">
+      <c r="I81" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>317</v>
-      </c>
       <c r="M81" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4944,40 +4941,40 @@
         <v>46277.482014710651</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="E82" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H82" s="3" t="s">
+      <c r="I82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="I82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J82" s="3" t="s">
+      <c r="K82" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L82" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="K82" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="M82" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4985,40 +4982,40 @@
         <v>46277.482562777775</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H83" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="M83" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5026,40 +5023,40 @@
         <v>46277.489715844902</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="3" t="s">
+      <c r="J84" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="J84" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="M84" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N84" s="3"/>
     </row>
@@ -5068,40 +5065,40 @@
         <v>46277.516303541663</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5109,40 +5106,40 @@
         <v>46277.722342789348</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G86" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H86" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="J86" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L86" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="M86" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N86" s="3"/>
     </row>
@@ -5151,40 +5148,40 @@
         <v>46277.800470335649</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="H87" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I87" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L87" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="M87" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N87" s="3"/>
     </row>
@@ -5193,40 +5190,40 @@
         <v>46277.891871921296</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J88" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L88" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="K88" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="M88" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5234,40 +5231,40 @@
         <v>46277.936662650463</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>342</v>
-      </c>
       <c r="M89" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N89" s="3"/>
     </row>
@@ -5276,40 +5273,40 @@
         <v>46278.29303184028</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C90" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="F90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J90" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J90" s="3" t="s">
+      <c r="K90" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L90" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="K90" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>347</v>
-      </c>
       <c r="M90" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N90" s="3"/>
     </row>
@@ -5318,40 +5315,40 @@
         <v>46278.772498946761</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K91" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>350</v>
-      </c>
       <c r="M91" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N91" s="3"/>
     </row>
@@ -5360,40 +5357,40 @@
         <v>46278.772688888886</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H92" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L92" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I92" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="M92" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N92" s="3"/>
     </row>
@@ -5402,40 +5399,40 @@
         <v>46278.786498680551</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N93" s="3"/>
     </row>
@@ -5444,40 +5441,40 @@
         <v>46278.789204872686</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C94" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H94" s="3" t="s">
+      <c r="I94" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="J94" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K94" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="M94" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N94" s="3"/>
     </row>
@@ -5486,40 +5483,40 @@
         <v>46278.794454895833</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C95" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N95" s="3"/>
     </row>
@@ -5528,40 +5525,40 @@
         <v>46278.794942997687</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C96" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D96" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N96" s="3"/>
     </row>
@@ -5570,40 +5567,40 @@
         <v>46278.823400370369</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I97" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I97" s="3" t="s">
+      <c r="J97" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L97" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="J97" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="M97" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5611,40 +5608,40 @@
         <v>46278.825915578709</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C98" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H98" s="3" t="s">
+      <c r="I98" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="J98" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="I98" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="J98" s="3" t="s">
+      <c r="K98" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L98" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="K98" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>366</v>
-      </c>
       <c r="M98" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5652,40 +5649,40 @@
         <v>46278.895070694445</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C99" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H99" s="3" t="s">
+      <c r="I99" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="I99" s="3" t="s">
+      <c r="J99" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L99" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="J99" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="M99" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N99" s="3"/>
     </row>
@@ -5694,40 +5691,40 @@
         <v>46278.902384467598</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C100" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="E100" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J100" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J100" s="3" t="s">
+      <c r="K100" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>374</v>
-      </c>
       <c r="M100" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5735,40 +5732,40 @@
         <v>46278.912840115736</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L101" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="M101" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N101" s="3"/>
     </row>
@@ -5777,40 +5774,40 @@
         <v>46278.921020532405</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N102" s="3"/>
     </row>
@@ -5819,40 +5816,40 @@
         <v>46278.922258032406</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N103" s="3"/>
     </row>
@@ -5861,40 +5858,40 @@
         <v>46278.923768020832</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N104" s="3"/>
     </row>
@@ -5903,40 +5900,40 @@
         <v>46278.984239884259</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E105" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H105" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H105" s="3" t="s">
+      <c r="I105" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L105" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="I105" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>384</v>
-      </c>
       <c r="M105" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5944,40 +5941,40 @@
         <v>46279.518157905091</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5985,40 +5982,40 @@
         <v>46279.640491331018</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6026,40 +6023,40 @@
         <v>46281.857825393519</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G108" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="H108" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6067,40 +6064,40 @@
         <v>46281.859266377316</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K109" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="L109" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="L109" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="M109" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N109" s="3"/>
     </row>
@@ -6109,40 +6106,40 @@
         <v>46283.472157581018</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H110" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L110" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="I110" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>390</v>
-      </c>
       <c r="M110" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N110" s="3"/>
     </row>
@@ -6151,40 +6148,40 @@
         <v>46283.836277175928</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K111" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N111" s="3"/>
     </row>
@@ -6193,40 +6190,122 @@
         <v>46283.876461446758</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H112" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="L112" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M112" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>46284.584563680561</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="I112" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L112" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M112" s="3" t="s">
-        <v>18</v>
+      <c r="D113" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K113" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="M113" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>46284.586728807873</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L114" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
